--- a/daily_matches/job_matches_2026-08-11.xlsx
+++ b/daily_matches/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Summer Intern 2027 - Data</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b2cebcf963c603</t>
+          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>West Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Apache Airflow, Git, PostgreSQL, MySQL, Tableau</t>
+          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, ChromaDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eece7ea708b14b8a</t>
+          <t>https://www.indeed.com/viewjob?jk=bad0281a6b90c24e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Sr. Bioinformatics Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>NYU Langone Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Git, Redshift, PySpark</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Apache Airflow, Git, PostgreSQL, MySQL, Tableau</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4e6f2c9965b8f46</t>
+          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>2027 Technology, Data, AI &amp; Ventures Summer Internship Program - Data Engineer Intern</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sequoia Connect</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, Glue, Athena, Redshift, Terraform, Git, Redshift, PySpark</t>
+          <t>AI Engineer, Data Scientist, RAG, Glue, Redshift, Git, Databricks, Redshift, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=798688cb780d9300</t>
+          <t>https://www.indeed.com/viewjob?jk=a7431d3f820412be</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lumen</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,192 +626,402 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kubernetes, AKS, CI/CD, Git, Databricks, PySpark, Kafka, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a0e61d2a772e99d</t>
+          <t>https://www.indeed.com/viewjob?jk=8c420ff855813ecf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>General Pipeline - FullStack Applied AI Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Infinity</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Prompt Engineering, BigQuery, FastAPI, BigQuery, PostgreSQL, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d95e996ac2d3bac8</t>
+          <t>https://www.indeed.com/viewjob?jk=e06a615a23db25ea</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Summer Intern 2027- Platform Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Mill, SC, US USA</t>
+          <t>Plantation, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9db38449e9a10df</t>
+          <t>https://www.indeed.com/viewjob?jk=39edb754f7dc273e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MSAT Scientist - Data Analyst</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lonza</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Vacaville, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Git, Tableau, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbdd953eb3ad01dd</t>
+          <t>https://www.indeed.com/viewjob?jk=9fe8e2a430f70c69</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer</t>
+          <t>Senior ML Platform Engineer - Healthcare AI &amp; Production Systems</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Inclusion Cloud</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, NoSQL, Power BI, SQL, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, AKS, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c9b3babc40a136c</t>
+          <t>https://www.indeed.com/viewjob?jk=16e09aa90c3a5318</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Advisor R&amp;D</t>
+          <t>2027 Technology, Data, AI &amp; Ventures Summer Internship Program - Data Scientist Intern</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Elanco</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Hypothesis Testing</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7b946c5e60d8f835</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Java AWS Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
         <v>10</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, TensorFlow, PyTorch, OpenCV, Git, Databricks, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29213f8e18a7d500</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Enabled QA Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b404fbd37d380583</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>VHB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Watertown, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Synapse, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0a712b9fb3c207</t>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Westlake, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Applied Genetics Scientist - Pipeline Data Science</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Syngenta</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Durham, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PyTorch, Keras, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08971e5f24294742</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4576f344147c7ba3</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-11.xlsx
+++ b/daily_matches/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, BigQuery, CI/CD, Git, BigQuery, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,269 +496,269 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce6090dbce36244c</t>
+          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>West Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, LangChain, RAG, LLaMA, Gemini, Copilot, Hugging Face, Pinecone, ChromaDB</t>
+          <t>Generative AI, RAG, Gemini, TensorFlow, BigQuery, CI/CD, Git, BigQuery, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad0281a6b90c24e</t>
+          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. Bioinformatics Developer</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NYU Langone Health</t>
+          <t>American business solutions inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Apache Airflow, Git, PostgreSQL, MySQL, Tableau</t>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fce382916bf426ff</t>
+          <t>https://www.indeed.com/viewjob?jk=76b56132a8962918</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2027 Technology, Data, AI &amp; Ventures Summer Internship Program - Data Engineer Intern</t>
+          <t>Cloud Engineer (Junior)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Glue, Redshift, Git, Databricks, Redshift, PostgreSQL, Python</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7431d3f820412be</t>
+          <t>https://www.indeed.com/viewjob?jk=d0ef116f7cdc9892</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c420ff855813ecf</t>
+          <t>https://www.indeed.com/viewjob?jk=16fdb2008f3dd9df</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Berwyn, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
+          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06a615a23db25ea</t>
+          <t>https://www.indeed.com/viewjob?jk=c7ee229456cf9f5c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>AI &amp; Automation Intern (Summer 2027)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Sargent &amp; Lundy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Plantation, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Matplotlib, Seaborn</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39edb754f7dc273e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a543f0537950207</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Cloud Engineer mid level</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Vidoori</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hyattsville, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, TensorFlow, PyTorch, Glue, Athena, Redshift, Redshift, Tableau, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9fe8e2a430f70c69</t>
+          <t>https://www.indeed.com/viewjob?jk=8a974ec190b285c4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior ML Platform Engineer - Healthcare AI &amp; Production Systems</t>
+          <t>Senior Investment Data Analyst, AI Enablement</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Kubernetes, AKS, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16e09aa90c3a5318</t>
+          <t>https://www.indeed.com/viewjob?jk=dc23163e641baf35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2027 Technology, Data, AI &amp; Ventures Summer Internship Program - Data Scientist Intern</t>
+          <t>Senior Backend Engineer - Scala / Play / Akka</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,42 +801,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Hypothesis Testing</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b946c5e60d8f835</t>
+          <t>https://www.indeed.com/viewjob?jk=ac4540db78bbf10b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Backend Engineer - Scala / Play / Akka</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, CI/CD, Terraform, Git, R, Java, Scala</t>
+          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29213f8e18a7d500</t>
+          <t>https://www.indeed.com/viewjob?jk=506de30ca8cae166</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Enabled QA Test Automation Engineer</t>
+          <t>Software Engineer III -Python Fullstack - AI/ML</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b404fbd37d380583</t>
+          <t>https://www.indeed.com/viewjob?jk=27356a493ed54411</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Analytics Engineer, GTM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VHB</t>
+          <t>Everpure</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Watertown, MA, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, Databricks, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Snowflake, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=633c0381a949d70e</t>
+          <t>https://www.indeed.com/viewjob?jk=67ae4b66132a4798</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Java Quality Engineer - (FTE / Onsite)</t>
+          <t>Full Stack Developer: Back End Focus</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,87 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, SQL, R, Java, Scala</t>
+          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20393355c09a2ba6</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Applied Genetics Scientist - Pipeline Data Science</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Syngenta</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Durham, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>10</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PyTorch, Keras, Docker, Kubernetes, NoSQL, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08971e5f24294742</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Terraform, Git, Snowflake, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4576f344147c7ba3</t>
+          <t>https://www.indeed.com/viewjob?jk=19e505d7e09cbb0b</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-11.xlsx
+++ b/daily_matches/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, BigQuery, CI/CD, Git, BigQuery, NoSQL, Python</t>
+          <t>S3, EC2, Glue, Redshift, Apache Airflow, CI/CD, Redshift, PySpark, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=129b88106a4533af</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, BigQuery, CI/CD, Git, BigQuery, NoSQL, Python</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50523aed281396ba</t>
+          <t>https://www.indeed.com/viewjob?jk=a73118e77870b1e5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Systems Engineer</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>American business solutions inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, PostgreSQL, MongoDB, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76b56132a8962918</t>
+          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Engineer (Junior)</t>
+          <t>Full Stack Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
+          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0ef116f7cdc9892</t>
+          <t>https://www.indeed.com/viewjob?jk=8b2b2537065fe4c3</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fdb2008f3dd9df</t>
+          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Berwyn, IL, US USA</t>
+          <t>Woonsocket, RI, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7ee229456cf9f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI &amp; Automation Intern (Summer 2027)</t>
+          <t>Quantitative Analytics Specialist (#001887)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sargent &amp; Lundy</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Git, Matplotlib, Seaborn</t>
+          <t>RAG, TensorFlow, XGBoost, LightGBM, Keras, Hadoop, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a543f0537950207</t>
+          <t>https://www.indeed.com/viewjob?jk=72c983bb2ac4eeab</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Cloud Engineer mid level</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vidoori</t>
+          <t>Knife River</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Hyattsville, MD, US USA</t>
+          <t>Bismarck, ND, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a974ec190b285c4</t>
+          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Investment Data Analyst, AI Enablement</t>
+          <t>Full-Stack Software Engineer - Remote Services</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>KLA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Git, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc23163e641baf35</t>
+          <t>https://www.indeed.com/viewjob?jk=3df4c5c94dbe995f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Scala / Play / Akka</t>
+          <t>AI Accelerated Senior Java Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Berkeley Heights, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
+          <t>Copilot, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac4540db78bbf10b</t>
+          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - Scala / Play / Akka</t>
+          <t>Digital Senior Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, Git, MySQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=506de30ca8cae166</t>
+          <t>https://www.indeed.com/viewjob?jk=6f2b46d5e3b60f71</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer III -Python Fullstack - AI/ML</t>
+          <t>Digital Senior Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27356a493ed54411</t>
+          <t>https://www.indeed.com/viewjob?jk=6be040cf5ea96b40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer, GTM</t>
+          <t>Digital Senior Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Everpure</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Snowflake, Tableau, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,14 +916,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67ae4b66132a4798</t>
+          <t>https://www.indeed.com/viewjob?jk=4a30feaae40d894f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer: Back End Focus</t>
+          <t>Agentic AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,25 +933,340 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, AWS SageMaker, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2de2c065ea762c91</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Technology Teacher at Islamic School: NYCMC Wellspring Schools</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>NYC Muslim Center</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Hollis, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=90cef56d93430def</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Woonsocket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, S3, Docker, CI/CD, GitHub Actions, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-07-16</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19e505d7e09cbb0b</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Woonsocket, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Richardson, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Scottsdale, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Engineer (Apps)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>WD</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, LLaMA, Hugging Face, CI/CD, Git, MySQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=049d55bf9fedded2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Embedded AI Engineer - Construction (Field Installation)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Gigapower</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>10</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=00bd0d8a584403cb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-11.xlsx
+++ b/daily_matches/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>S3, EC2, Glue, Redshift, Apache Airflow, CI/CD, Redshift, PySpark, NoSQL, Python</t>
+          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb3140ee1f47831</t>
+          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Informatics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Prime Medicine</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, Kafka, NoSQL, SQL</t>
+          <t>LangChain, RAG, Copilot, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a73118e77870b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Embedded AI Engineer - IT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7837fd5164e6a44</t>
+          <t>https://www.indeed.com/viewjob?jk=5fc886e126c62e97</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Senior Software Engineer</t>
+          <t>Data Engineer - AI, Agents, &amp; Context - Revenue Cycle (Associate)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Huron Consulting Group</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R, Java</t>
+          <t>AI Engineer, RAG, Pinecone, Snowflake, Power BI, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b2b2537065fe4c3</t>
+          <t>https://www.indeed.com/viewjob?jk=49403d9509cfbccf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Embedded AI Engineer - Finance</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8a888f4e8d3b768</t>
+          <t>https://www.indeed.com/viewjob?jk=287db358dfc3dcf3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE, Retail &amp; Pharmacy</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Valence</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Woonsocket, RI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89da70fdb2d97367</t>
+          <t>https://www.indeed.com/viewjob?jk=297d703e7a2ce828</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Quantitative Analytics Specialist (#001887)</t>
+          <t>Full Time- Graduate Development Program-AI &amp; Analytics Associate-Nashville, TN or Cambridge, MA-2027</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Philips</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, XGBoost, LightGBM, Keras, Hadoop, Python, SQL, R, Java</t>
+          <t>Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72c983bb2ac4eeab</t>
+          <t>https://www.indeed.com/viewjob?jk=f78b8ee944f14b20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>AI Engineer (Dublin, CA or USA Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Knife River</t>
+          <t>SavvyMoney</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bismarck, ND, US USA</t>
+          <t>Dublin, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, SQL</t>
+          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, MLflow, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=113d33b7673b9bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=cc25cadbf645050d</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer - Remote Services</t>
+          <t>Senior AI Engineer – Agentic Solutions &amp; Digital Thread</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KLA</t>
+          <t>Moog, Inc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Docker, Kubernetes, CI/CD, Git, R, Java, Scala</t>
+          <t>AI Engineer, LangChain, RAG, CI/CD, Git, Databricks, Kafka, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df4c5c94dbe995f</t>
+          <t>https://www.indeed.com/viewjob?jk=df8f65d67a866926</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI Accelerated Senior Java Engineer</t>
+          <t>Embedded AI Engineer - Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Berkeley Heights, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, Kubernetes, CI/CD, Jenkins, Git, MySQL, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a415b08ffa069b7f</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe1cd8b08f987c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Digital Senior Development Engineer</t>
+          <t>Embedded AI Engineer - Construction (Project Management)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f2b46d5e3b60f71</t>
+          <t>https://www.indeed.com/viewjob?jk=4889ad8363cb115a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Digital Senior Development Engineer</t>
+          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Orion180 Insurance Services, LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6be040cf5ea96b40</t>
+          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Digital Senior Development Engineer</t>
+          <t>Development Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bullhorn</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, CI/CD, Jenkins, GitHub Actions, Git, R, Java, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a30feaae40d894f</t>
+          <t>https://www.indeed.com/viewjob?jk=235583fee29e3842</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Agentic AI</t>
+          <t>Senior Analyst, Onboard Revenue (CCL)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Carnival Cruise Line</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, TensorFlow, AWS SageMaker, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,322 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2de2c065ea762c91</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Technology Teacher at Islamic School: NYCMC Wellspring Schools</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NYC Muslim Center</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Hollis, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D16" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, Prompt Engineering, TensorFlow, PyTorch, Git, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=90cef56d93430def</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Woonsocket, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9a6b395659de2d05</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>10</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29deca2ea5145f06</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Woonsocket, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>10</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a472f23e1c340c70</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>10</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2978763d135cc0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Richardson, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39f2465d623c26d1</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - SRE, Retail and Pharmacy</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>CVS Health</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Scottsdale, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, Terraform, Kafka, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc1394ccb8124c7</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer (Apps)</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>WD</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, LLaMA, Hugging Face, CI/CD, Git, MySQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=049d55bf9fedded2</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Embedded AI Engineer - Construction (Field Installation)</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Gigapower</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00bd0d8a584403cb</t>
+          <t>https://www.indeed.com/viewjob?jk=cedcaad43baa3f06</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-11.xlsx
+++ b/daily_matches/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9225336bad1dc9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Informatics Engineer</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Prime Medicine</t>
+          <t>AmeriSave Mortgage</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Copilot, Docker, AKS, CI/CD, Terraform, Git, PostgreSQL, Python</t>
+          <t>Data Scientist, LangChain, RAG, Mistral, Hugging Face, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbd24beae107df7e</t>
+          <t>https://www.indeed.com/viewjob?jk=2699965a5b01cf03</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Embedded AI Engineer - IT</t>
+          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Cortex, Synapse, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fc886e126c62e97</t>
+          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer - AI, Agents, &amp; Context - Revenue Cycle (Associate)</t>
+          <t>AI Consultant</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Huron Consulting Group</t>
+          <t>UNICON SYSTEMS</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Pinecone, Snowflake, Power BI, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49403d9509cfbccf</t>
+          <t>https://www.indeed.com/viewjob?jk=18f03b997f5ee7ed</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Embedded AI Engineer - Finance</t>
+          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>UnitedHealthcare</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>AI Engineer, Data Scientist, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287db358dfc3dcf3</t>
+          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Embedded AI Engineer - Supply Chain &amp; Admin</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Valence</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,19 +671,19 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=297d703e7a2ce828</t>
+          <t>https://www.indeed.com/viewjob?jk=d19c9ebd561d22f6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Time- Graduate Development Program-AI &amp; Analytics Associate-Nashville, TN or Cambridge, MA-2027</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Philips</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, Git, Power BI, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f78b8ee944f14b20</t>
+          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer (Dublin, CA or USA Remote)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SavvyMoney</t>
+          <t>FDM Group</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dublin, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Copilot, Prompt Engineering, MLflow, Git, Python, R, Scala</t>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc25cadbf645050d</t>
+          <t>https://www.indeed.com/viewjob?jk=4de46d944f61b7a4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior AI Engineer – Agentic Solutions &amp; Digital Thread</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Moog, Inc</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, CI/CD, Git, Databricks, Kafka, Python, R, Scala</t>
+          <t>RAG, Copilot, CI/CD, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df8f65d67a866926</t>
+          <t>https://www.indeed.com/viewjob?jk=bfee8059c6dbc176</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Embedded AI Engineer - Engineering</t>
+          <t>Software Engineer in Test</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>PatientPoint</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe1cd8b08f987c6</t>
+          <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Embedded AI Engineer - Construction (Project Management)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
+          <t>Generative AI, RAG, Gemini, S3, Apache Airflow, Git, Snowflake, SQL, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4889ad8363cb115a</t>
+          <t>https://www.indeed.com/viewjob?jk=b24e1c655a73535b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer (PowerBi and Fabric)</t>
+          <t>Business Systems Analyst 2 (NY HELPS), SG-23 Vacancy ID #221623</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Orion180 Insurance Services, LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Snowflake, Databricks, Power BI, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, Git, PostgreSQL, MySQL, NoSQL, Tableau, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5f974f63b3e098a</t>
+          <t>https://www.indeed.com/viewjob?jk=09c62a2a994eda77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Development Operations Engineer</t>
+          <t>Data Scientist, Finance</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bullhorn</t>
+          <t>Ramp</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,42 +916,322 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=235583fee29e3842</t>
+          <t>https://www.indeed.com/viewjob?jk=0c1a820ab3563948</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Analyst, Onboard Revenue (CCL)</t>
+          <t>Temporary Research Intelligence Data Science Specialist</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Carnival Cruise Line</t>
+          <t>Univeristy Of Colorado Boulder</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, FastAPI, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e9a61055ff89f354</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Senior Technical Consultant - Microsoft Power Platform</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Ahead</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Tableau, Power BI, SQL, R, Scala, Optimization, Hypothesis Testing</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cedcaad43baa3f06</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88b3b87de19aec1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer II</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Bank of America</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Jenkins, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9759d3d153d8910e</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>AI Voice Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Nowcom, LLC</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=621dd17220c454a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Cloud Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VIVA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Technical Consultant - Microsoft Power Platform</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Ahead</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9e223ce57c1339aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Student Worker - Machine Learning Engineer - Data Mining &amp; VLM</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Zoox</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>10</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, RAG, Git, PySpark, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=02074ebb9a9808b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>10</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=754c2049238d49f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - Engineering Analysis Automation</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>10</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>RAG, EC2, Docker, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=578ef2c734d99847</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-11.xlsx
+++ b/daily_matches/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>23.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Jenkins, Git</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b72188bd56c0e1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>AI Engineer (LLMs + C#)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AmeriSave Mortgage</t>
+          <t>Aperia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>23.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Mistral, Hugging Face, Pinecone, Prompt Engineering, FastAPI, Docker, CI/CD</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2699965a5b01cf03</t>
+          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Enterprise Data Warehouse - Remote</t>
+          <t>Predictive &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bright MLS, Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Cortex, Synapse, Data Lake, Git, Snowflake, Databricks, Tableau, Power BI</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8c7ee86ade96fc0</t>
+          <t>https://www.indeed.com/viewjob?jk=68bc3e08f09bb3ed</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Consultant</t>
+          <t>Predictive &amp; Agentic AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>UNICON SYSTEMS</t>
+          <t>Bright MLS, Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>North Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>22.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, CI/CD, Git, Snowflake, Databricks, Python, R</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18f03b997f5ee7ed</t>
+          <t>https://www.indeed.com/viewjob?jk=685ab3fb5abe00cc</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Data Scientist - AI or ML Engineering Focus - Remote</t>
+          <t>CT_NITRO Experimental AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>UnitedHealthcare</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, MLflow, CI/CD, GitHub Actions, Git, Databricks, PySpark, Kafka, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, Docker, AKS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be573081e3bdbe94</t>
+          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Embedded AI Engineer - Supply Chain &amp; Admin</t>
+          <t>Senior . Net Backend Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Copilot, Prompt Engineering, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d19c9ebd561d22f6</t>
+          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Python Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Java</t>
+          <t>LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=127b8ee0d5e8b7d6</t>
+          <t>https://www.indeed.com/viewjob?jk=89278ffae7111ddc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Enterprise Intelligence Solutions Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>FDM Group</t>
+          <t>Freedom Mortgage</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Marlton, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java, Optimization</t>
+          <t>Generative AI, RAG, Copilot, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de46d944f61b7a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d5a216e8583406db</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Software Engineer - EMC Life</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>EMC Insurance</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, Git, MongoDB, NoSQL, Python, SQL, R, Scala</t>
+          <t>RAG, Gemini, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfee8059c6dbc176</t>
+          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer in Test</t>
+          <t>AI &amp; Distributed Systems Fullstack Engineer - Senior - Consulting - Location OPEN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PatientPoint</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copilot, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, MySQL, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, FastAPI, AKS, Git, PostgreSQL, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=597c1235384c626f</t>
+          <t>https://www.indeed.com/viewjob?jk=4eac196eb5845610</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cybersecurity - AI Cybersecurity Architect &amp; Engineer - Consulting - Location OPEN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>EY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, S3, Apache Airflow, Git, Snowflake, SQL, R, Java</t>
+          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, AKS, Python</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b24e1c655a73535b</t>
+          <t>https://www.indeed.com/viewjob?jk=11aa8dddad9ac22a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Business Systems Analyst 2 (NY HELPS), SG-23 Vacancy ID #221623</t>
+          <t>Agent Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Rifa AI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Git, PostgreSQL, MySQL, NoSQL, Tableau, Python, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, FastAPI, Kubernetes, AKS, Git, PostgreSQL, Seaborn, Python, SQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09c62a2a994eda77</t>
+          <t>https://www.indeed.com/viewjob?jk=66071b963c1c668b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist, Finance</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c1a820ab3563948</t>
+          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Temporary Research Intelligence Data Science Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Univeristy Of Colorado Boulder</t>
+          <t>Gigapower</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, FastAPI, Snowflake, BigQuery, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9a61055ff89f354</t>
+          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Microsoft Power Platform</t>
+          <t>Data and Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>State of Kansas</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, Data Lake, MLflow, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b3b87de19aec1a</t>
+          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>Nexxen</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kubernetes, CI/CD, Jenkins, Terraform, PostgreSQL, Cassandra, Python, SQL, R</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9759d3d153d8910e</t>
+          <t>https://www.indeed.com/viewjob?jk=280370f0bb800cfb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Voice Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nowcom, LLC</t>
+          <t>Nexxen</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Python, R, Scala</t>
+          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=621dd17220c454a4</t>
+          <t>https://www.indeed.com/viewjob?jk=eaea3c89a12945f9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Kubernetes, CI/CD, Terraform, Git, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10e3305971e0ebf9</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c80a2aa27674d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Technical Consultant - Microsoft Power Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ahead</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Git, Power BI, Python, SQL, R, Java, Optimization</t>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, MongoDB, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e223ce57c1339aa</t>
+          <t>https://www.indeed.com/viewjob?jk=15ccdfb6af12e7c0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Student Worker - Machine Learning Engineer - Data Mining &amp; VLM</t>
+          <t>Windows Systems Automation Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, Git, PySpark, Python, SQL, R, Scala, Optimization</t>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02074ebb9a9808b8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a45ae3acda1a172</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Engineer, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>10</v>
+        <v>11.1</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,462 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=754c2049238d49f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Engineering Analysis Automation</t>
+          <t>Applied AI Engineer, Office of the CEO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Pagaya Investments</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, Tableau, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d58f01c8ce539a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Cloud DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Texas Health and Human Services Commission</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b9eb0bbee0c294df</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Full-Stack Data Engineer</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>The Hearst Corporation</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Troy, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Glue, Redshift, Kubernetes, CI/CD, Git, Databricks, Redshift, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Alexandria, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>accrete</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Consulting - Tech Consulting - FinTech - FSO, Blockchain and AI Engineering - Senior</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Docker, Kubernetes, AKS, Terraform, Git, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85ba511a6f58d6b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Data Scientist, Finance</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db9ea7da2840ae2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Data Scientist, Finance</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Ramp</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ca1321078ee38939</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
         <v>10</v>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, EC2, Docker, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=578ef2c734d99847</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=082da079918ccf38</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Applied AI Engineer</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Gigapower</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=859b8437626dcae2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AI/LLM Engineer</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d55998e51d5e754</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Data Analyst/Engineer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Quest Global</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0b30705b271aa209</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Hadoop, NoSQL, Tableau, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=932136374fd96407</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-08-11.xlsx
+++ b/daily_matches/job_matches_2026-08-11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Senior Data Science Engineer (With TS/SCI Clearance and a current Full Scope Poly)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>J&amp;T Business Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Annapolis Junction, MD, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>24.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, XGBoost, Azure ML, MLflow, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f997656e9e4686</t>
+          <t>https://www.indeed.com/viewjob?jk=e904a72543c1613d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Engineer (LLMs + C#)</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aperia</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>23.3</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, Kubernetes</t>
+          <t>RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03e97eecd14f0fb3</t>
+          <t>https://www.indeed.com/viewjob?jk=bc9ea64b3e0c74c1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Predictive &amp; Agentic AI Engineer</t>
+          <t>Partner Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bright MLS, Inc</t>
+          <t>Striim</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Gemini, Copilot, BigQuery, Docker, Kubernetes, Git, Snowflake, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68bc3e08f09bb3ed</t>
+          <t>https://www.indeed.com/viewjob?jk=41afaba58e1c4224</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Predictive &amp; Agentic AI Engineer</t>
+          <t>Summer Intern 2027 - Data</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bright MLS, Inc</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>North Bethesda, MD, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22.2</v>
+        <v>17.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Gemini, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Generative AI, RAG, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=685ab3fb5abe00cc</t>
+          <t>https://www.indeed.com/viewjob?jk=5ac3317abd73d3aa</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CT_NITRO Experimental AI Engineer</t>
+          <t>Software Engineer 2 (AI/GenAI)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Earth City, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Keras, Docker, AKS</t>
+          <t>LangChain, RAG, Copilot, Prompt Engineering, FastAPI, Docker, Kubernetes, CI/CD, Git, PostgreSQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa276c48188a3cea</t>
+          <t>https://www.indeed.com/viewjob?jk=352496db659a2a8d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior . Net Backend Software Engineer</t>
+          <t>Data Engineer III - Python, Databricks</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cloud and Things</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>17.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, NoSQL</t>
+          <t>RAG, Copilot, Prompt Engineering, Glue, Data Lake, Docker, CI/CD, Git, Databricks, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24aad05f5ee2e0c</t>
+          <t>https://www.indeed.com/viewjob?jk=31e94d86522e8759</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Python Full Stack Engineer</t>
+          <t>Remote Snowflake Certified Architect / Senior Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>MindBoard</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LangChain, RAG, Prompt Engineering, FastAPI, CI/CD, GitHub Actions, Git, NoSQL, Python, SQL</t>
+          <t>RAG, Glue, Docker, Kubernetes, CI/CD, Git, Snowflake, Kafka, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89278ffae7111ddc</t>
+          <t>https://www.indeed.com/viewjob?jk=7652a87536a73d6b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Enterprise Intelligence Solutions Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Freedom Mortgage</t>
+          <t>Tempus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Marlton, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Snowflake, Databricks, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5a216e8583406db</t>
+          <t>https://www.indeed.com/viewjob?jk=4e6d943817d3d85c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - EMC Life</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EMC Insurance</t>
+          <t>Wheeler Machinery Co</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Gemini, Copilot, CI/CD, Terraform, Git, NoSQL, Python, SQL, R</t>
+          <t>RAG, Copilot, S3, Docker, CI/CD, GitHub Actions, Terraform, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92f160b74d66c67</t>
+          <t>https://www.indeed.com/viewjob?jk=a6d849ae42553189</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AI &amp; Distributed Systems Fullstack Engineer - Senior - Consulting - Location OPEN</t>
+          <t>Software Engineer - Data Center</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>SpaceXAI</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,69 +801,69 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, FastAPI, AKS, Git, PostgreSQL, Tableau, Python, SQL</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, MySQL, MongoDB, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eac196eb5845610</t>
+          <t>https://www.indeed.com/viewjob?jk=1b4ea598fe484112</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Cybersecurity - AI Cybersecurity Architect &amp; Engineer - Consulting - Location OPEN</t>
+          <t>Senior Software Engineer - App Reliability</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>MetLife</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cary, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Kubernetes, AKS, Python</t>
+          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11aa8dddad9ac22a</t>
+          <t>https://www.indeed.com/viewjob?jk=f3473cf07214c5ee</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Agent Engineer</t>
+          <t>EDP Cloud Systems Engineer – Washington, DC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Rifa AI</t>
+          <t>Creative Information Technology India</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Falls Church, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, FastAPI, Kubernetes, AKS, Git, PostgreSQL, Seaborn, Python, SQL</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66071b963c1c668b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4e97627506b5d28</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - App Reliability</t>
+          <t>Sr Data Scientist</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>Electronic Arts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, MongoDB, Python, R, Java</t>
+          <t>Data Scientist, RAG, Kubernetes, Snowflake, Databricks, Kafka, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec9965e5f979d25</t>
+          <t>https://www.indeed.com/viewjob?jk=1b97ef9ad96dfc39</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Customer Success Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>Britive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68de453c48c65af</t>
+          <t>https://www.indeed.com/viewjob?jk=de2fdd477c52ce50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>State of Kansas</t>
+          <t>Buildertrend</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, MLflow, CI/CD, Git, Databricks, Tableau, Power BI, Python, SQL</t>
+          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, MongoDB, Tableau, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b23d350c0a1037</t>
+          <t>https://www.indeed.com/viewjob?jk=6a0d83ad41e4c629</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Gemini, S3, Apache Airflow, Git, Snowflake, SQL, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=280370f0bb800cfb</t>
+          <t>https://www.indeed.com/viewjob?jk=2b42cf9fbbc1ddb9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Windows Systems Automation Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nexxen</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Data Scientist, TensorFlow, PyTorch, Keras, Git, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eaea3c89a12945f9</t>
+          <t>https://www.indeed.com/viewjob?jk=435b9e1000e86233</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Remote</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DriveTime Automotive Group</t>
+          <t>Johnson Controls</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Snowflake, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c80a2aa27674d</t>
+          <t>https://www.indeed.com/viewjob?jk=6eb7ec7147a9b582</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Applied AI Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Buildertrend</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Snowflake, Databricks, BigQuery, MongoDB, Tableau, Python, SQL, R</t>
+          <t>RAG, Copilot, CI/CD, Git, MongoDB, NoSQL, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15ccdfb6af12e7c0</t>
+          <t>https://www.indeed.com/viewjob?jk=8eea3eb45eaec39e</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Windows Systems Automation Engineer</t>
+          <t>Summer Intern 2027- Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, CI/CD, Terraform, Git, PostgreSQL, MongoDB, SQL, R</t>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a45ae3acda1a172</t>
+          <t>https://www.indeed.com/viewjob?jk=863bd725a75434fe</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, PDS&amp;T CMC</t>
+          <t>Senior Software Engineer - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>DriveTime Automotive Group</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Glue, CI/CD, Snowflake, Databricks, Python, SQL, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Snowflake, Kafka, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c963aa2f5440dd5a</t>
+          <t>https://www.indeed.com/viewjob?jk=e27ac45b7ca2fb31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Applied AI Engineer, Office of the CEO</t>
+          <t>Platform Engineer (Senior)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Pagaya Investments</t>
+          <t>Rifa AI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, Tableau, Python, SQL, R, Java, Scala</t>
+          <t>RAG, FastAPI, Kubernetes, CI/CD, Git, PostgreSQL, Seaborn, Python, SQL, R</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d58f01c8ce539a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec0a0b8df192d16b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Software Developer, Advanced</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Schenectady, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9eb0bbee0c294df</t>
+          <t>https://www.indeed.com/viewjob?jk=550170aeab2dbe5d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Full-Stack Data Engineer</t>
+          <t>Software Developer, Advanced</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>The Hearst Corporation</t>
+          <t>Naval Nuclear Laboratory</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Troy, MI, US USA</t>
+          <t>West Mifflin, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glue, Redshift, Kubernetes, CI/CD, Git, Databricks, Redshift, Python, SQL, R</t>
+          <t>Copilot, Azure ML, Data Lake, CI/CD, Git, Power BI, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f64121baa0dd81b4</t>
+          <t>https://www.indeed.com/viewjob?jk=6616fe8cc01910c7</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr Scientist, Tech</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Uber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Alexandria, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>PySpark, Hadoop, Tableau, Matplotlib, Python, SQL, R, Scala, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3f545fc0176e351</t>
+          <t>https://www.indeed.com/viewjob?jk=819f2fd1e05a2840</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>CCB Risk Modeling - AI ML Sr. Associate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,64 +1361,64 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Prompt Engineering, TensorFlow, PyTorch, XGBoost, Git, Hadoop, Python, R, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ec121a9fa254deb</t>
+          <t>https://www.indeed.com/viewjob?jk=be0040a56eb930c0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Consulting - Tech Consulting - FinTech - FSO, Blockchain and AI Engineering - Senior</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Camping World</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lincolnshire, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, AKS, Terraform, Git, R, Java, Scala</t>
+          <t>RAG, Gemini, Copilot, AKS, CI/CD, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85ba511a6f58d6b7</t>
+          <t>https://www.indeed.com/viewjob?jk=d4e2ec77ebff4141</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Scientist, Finance</t>
+          <t>Fullstack Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>Samba TV</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>AI Engineer, RAG, CI/CD, Git, PostgreSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db9ea7da2840ae2c</t>
+          <t>https://www.indeed.com/viewjob?jk=42f17515af04acb3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Scientist, Finance</t>
+          <t>Full-Stack Java React Software Engineer III</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ramp</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Redshift, BigQuery, Snowflake, BigQuery, Redshift, SQL, R, Scala</t>
+          <t>RAG, S3, Docker, Kubernetes, CI/CD, Databricks, R, Java, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca1321078ee38939</t>
+          <t>https://www.indeed.com/viewjob?jk=5fdd361c4932d24d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Sr. Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Commence</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Virginia Beach, VA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, TensorFlow, PyTorch, Python, R, Java, Scala</t>
+          <t>RAG, S3, CI/CD, Jenkins, GitHub Actions, Git, NoSQL, SQL, R</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=082da079918ccf38</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7216e95a38186a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Applied AI Engineer</t>
+          <t>Software Engineer III- Eng</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Gigapower</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,122 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, CI/CD, Git, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, CI/CD, GitHub Actions, Git, Python, R, Java, Optimization</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=859b8437626dcae2</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>AI/LLM Engineer</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, Git, Python, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d55998e51d5e754</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Data Analyst/Engineer</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Quest Global</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Data Lake, Git, Snowflake, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0b30705b271aa209</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Scientist II</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Scientist, Hadoop, NoSQL, Tableau, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=932136374fd96407</t>
+          <t>https://www.indeed.com/viewjob?jk=4166313632556681</t>
         </is>
       </c>
     </row>
